--- a/QUOTATION_EXCEL_TEMPLATES/kr_la_sea/KR_LA_SEA_2026_QUOTATION.xlsx
+++ b/QUOTATION_EXCEL_TEMPLATES/kr_la_sea/KR_LA_SEA_2026_QUOTATION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\다른 컴퓨터\내 컴퓨터\LK Group 관련\1. 한국-라오 해상 관련\고객 견적 확인 요청건\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\QUOTATION_EXCEL_TEMPLATES\kr_la_sea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE230A-B91F-4688-ACD5-7B31C85E184E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348042DB-1499-4017-97D9-C8D398214481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="0" windowWidth="17952" windowHeight="12084" tabRatio="908" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1005" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
@@ -1228,10 +1228,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Kor-Lao Sea 가견적</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>* 물품 도착 및 출고 후 특별한 사유 없이 장기 미수취 물품의 경우 보관료등 기타 추가 비용이 발생 할 수 있습니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1243,6 +1239,10 @@
     <t>- 동 가견적 운임의 중량 및 크기는 단순 예상치이므로 최종 책정 방법인 기준인 실측시 금액 차이가 발생 할수 있으니, 참고용으로만 확인 부탁 드립니다.
 - 운임은 USD 기준이며, 이외 화폐는 가견적 안내시의 환율 기준이므로, 최종 운임 책정시의 환율변동으로 인한 운임 차이가 발생할수 있으니, 참고용으로만 확인 부탁 드립니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kor-Lao Sea 가견적서</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2073,12 +2073,123 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2118,136 +2229,25 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2333,7 +2333,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$13:$F$33" spid="_x0000_s103721"/>
+                  <a14:cameraTool cellRange="$A$13:$F$33" spid="_x0000_s103722"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2547,8 +2547,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="50800" y="15240000"/>
-          <a:ext cx="7899400" cy="3733800"/>
+          <a:off x="50800" y="15925800"/>
+          <a:ext cx="7931150" cy="3727450"/>
           <a:chOff x="50800" y="15240000"/>
           <a:chExt cx="7899400" cy="3733800"/>
         </a:xfrm>
@@ -2679,8 +2679,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9931400" y="15214600"/>
-          <a:ext cx="7975600" cy="3719369"/>
+          <a:off x="9963150" y="15900400"/>
+          <a:ext cx="8020050" cy="3719369"/>
           <a:chOff x="9118600" y="15214600"/>
           <a:chExt cx="7975600" cy="3719369"/>
         </a:xfrm>
@@ -2817,8 +2817,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="19862800" y="15214599"/>
-          <a:ext cx="8026400" cy="3747978"/>
+          <a:off x="19945350" y="15900399"/>
+          <a:ext cx="8039100" cy="3747978"/>
           <a:chOff x="19761200" y="15214599"/>
           <a:chExt cx="8026400" cy="3747978"/>
         </a:xfrm>
@@ -2957,7 +2957,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$34" spid="_x0000_s102855"/>
+                  <a14:cameraTool cellRange="$A$1:$N$34" spid="_x0000_s102856"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -3345,55 +3345,55 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:AD68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="4" style="35" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.8984375" style="35" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="35" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="35" customWidth="1"/>
     <col min="5" max="5" width="14.5" style="35" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" style="35" customWidth="1"/>
-    <col min="7" max="7" width="6.09765625" style="35" customWidth="1"/>
+    <col min="7" max="7" width="6.125" style="35" customWidth="1"/>
     <col min="8" max="8" width="15" style="50" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.59765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.8984375" style="50" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" style="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.875" style="50" customWidth="1"/>
     <col min="14" max="14" width="15.5" style="50" customWidth="1"/>
-    <col min="15" max="15" width="9.8984375" style="50" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.09765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.19921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.09765625" style="50" customWidth="1"/>
-    <col min="21" max="21" width="34.19921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.875" style="50" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.125" style="50" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.25" style="50" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.125" style="50" customWidth="1"/>
+    <col min="21" max="21" width="34.25" style="50" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.75" style="50" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="38.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.19921875" style="50" customWidth="1"/>
+    <col min="26" max="26" width="4.25" style="50" customWidth="1"/>
     <col min="27" max="27" width="22" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.8984375" style="50" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.3984375" style="50" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.875" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.375" style="50" bestFit="1" customWidth="1"/>
     <col min="31" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:25">
-      <c r="B1" s="142" t="s">
+      <c r="B1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="H1" s="145" t="s">
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="H1" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
     </row>
     <row r="2" spans="2:25">
       <c r="B2" s="36" t="s">
@@ -3457,30 +3457,30 @@
         <f>C4+D4</f>
         <v>34</v>
       </c>
-      <c r="H4" s="146" t="s">
+      <c r="H4" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="147"/>
-      <c r="J4" s="146" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="147"/>
-      <c r="N4" s="146" t="s">
+      <c r="K4" s="142"/>
+      <c r="N4" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="147"/>
-      <c r="P4" s="146" t="s">
+      <c r="O4" s="142"/>
+      <c r="P4" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="147"/>
-      <c r="U4" s="146" t="s">
+      <c r="Q4" s="142"/>
+      <c r="U4" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="V4" s="147"/>
-      <c r="W4" s="146" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="X4" s="147"/>
+      <c r="X4" s="142"/>
     </row>
     <row r="5" spans="2:25">
       <c r="B5" s="42" t="s">
@@ -3572,12 +3572,12 @@
       </c>
     </row>
     <row r="8" spans="2:25">
-      <c r="B8" s="144" t="s">
+      <c r="B8" s="146" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
+      <c r="C8" s="146"/>
+      <c r="D8" s="146"/>
+      <c r="E8" s="146"/>
       <c r="H8" s="36" t="s">
         <v>40</v>
       </c>
@@ -3622,12 +3622,12 @@
       </c>
     </row>
     <row r="9" spans="2:25">
-      <c r="B9" s="144" t="s">
+      <c r="B9" s="146" t="s">
         <v>280</v>
       </c>
-      <c r="C9" s="144"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="144"/>
+      <c r="C9" s="146"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="146"/>
       <c r="H9" s="36" t="s">
         <v>57</v>
       </c>
@@ -4231,11 +4231,11 @@
       </c>
       <c r="R24" s="59"/>
       <c r="S24" s="59"/>
-      <c r="U24" s="141" t="s">
+      <c r="U24" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="V24" s="141"/>
-      <c r="W24" s="141"/>
+      <c r="V24" s="144"/>
+      <c r="W24" s="144"/>
       <c r="X24" s="59">
         <f>SUM(X9:X23)</f>
         <v>0</v>
@@ -4368,7 +4368,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="29" spans="2:25" ht="38.4">
+    <row r="29" spans="2:25" ht="34.5">
       <c r="D29" s="61">
         <f>SUM(D23:D28)</f>
         <v>0</v>
@@ -4603,11 +4603,11 @@
       </c>
       <c r="R35" s="59"/>
       <c r="S35" s="59"/>
-      <c r="U35" s="141" t="s">
+      <c r="U35" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="V35" s="141"/>
-      <c r="W35" s="141"/>
+      <c r="V35" s="144"/>
+      <c r="W35" s="144"/>
       <c r="X35" s="59">
         <f>SUM(X29:X34)</f>
         <v>0</v>
@@ -4958,12 +4958,12 @@
       </c>
       <c r="K46" s="54"/>
       <c r="L46" s="54"/>
-      <c r="N46" s="141" t="s">
+      <c r="N46" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="O46" s="141"/>
-      <c r="P46" s="141"/>
-      <c r="Q46" s="141"/>
+      <c r="O46" s="144"/>
+      <c r="P46" s="144"/>
+      <c r="Q46" s="144"/>
       <c r="R46" s="54">
         <f>SUM(R9:R45)</f>
         <v>0</v>
@@ -4981,7 +4981,7 @@
       <c r="X46" s="36"/>
       <c r="Y46" s="36"/>
     </row>
-    <row r="47" spans="8:25" ht="38.4">
+    <row r="47" spans="8:25" ht="34.5">
       <c r="H47" s="36" t="s">
         <v>66</v>
       </c>
@@ -5101,11 +5101,11 @@
       </c>
       <c r="K52" s="54"/>
       <c r="L52" s="54"/>
-      <c r="U52" s="141" t="s">
+      <c r="U52" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="V52" s="141"/>
-      <c r="W52" s="141"/>
+      <c r="V52" s="144"/>
+      <c r="W52" s="144"/>
       <c r="X52" s="59">
         <f>SUM(X40:X51)</f>
         <v>0</v>
@@ -5266,7 +5266,7 @@
       <c r="X61" s="36"/>
       <c r="Y61" s="36"/>
     </row>
-    <row r="62" spans="8:25" ht="38.4">
+    <row r="62" spans="8:25" ht="34.5">
       <c r="H62" s="88" t="s">
         <v>278</v>
       </c>
@@ -5323,11 +5323,11 @@
       <c r="Y65" s="48"/>
     </row>
     <row r="66" spans="8:25">
-      <c r="H66" s="141" t="s">
+      <c r="H66" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="I66" s="141"/>
-      <c r="J66" s="141"/>
+      <c r="I66" s="144"/>
+      <c r="J66" s="144"/>
       <c r="K66" s="57">
         <f>SUM(K9:K65)</f>
         <v>0</v>
@@ -5347,11 +5347,11 @@
       <c r="Y67" s="48"/>
     </row>
     <row r="68" spans="8:25">
-      <c r="U68" s="141" t="s">
+      <c r="U68" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="V68" s="141"/>
-      <c r="W68" s="141"/>
+      <c r="V68" s="144"/>
+      <c r="W68" s="144"/>
       <c r="X68" s="59">
         <f>SUM(X57:X67)</f>
         <v>0</v>
@@ -5365,12 +5365,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="22">
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="N46:Q46"/>
-    <mergeCell ref="U55:X55"/>
     <mergeCell ref="U68:W68"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="H3:K3"/>
@@ -5387,6 +5381,12 @@
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="N46:Q46"/>
+    <mergeCell ref="U55:X55"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5403,48 +5403,48 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="28.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.3984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.3984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="51.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.8984375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="39.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="39.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="51.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="49.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="46.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="30.8984375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="30.875" style="1" customWidth="1"/>
     <col min="19" max="19" width="9" style="1"/>
-    <col min="20" max="23" width="36.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="36.375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="103" t="s">
-        <v>286</v>
-      </c>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
+      <c r="C1" s="140" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
       <c r="L1" s="77" t="s">
         <v>203</v>
       </c>
-      <c r="M1" s="89" t="str">
+      <c r="M1" s="127" t="str">
         <f ca="1">IFERROR(INDEX(#REF!,MATCH(N2,#REF!,0),3)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="N1" s="89"/>
+      <c r="N1" s="127"/>
       <c r="R1" s="23">
         <f ca="1">D16</f>
         <v>1</v>
@@ -5462,34 +5462,34 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="43.8">
+    <row r="2" spans="1:23" s="2" customFormat="1" ht="45">
       <c r="A2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="90"/>
+      <c r="C2" s="111"/>
       <c r="D2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="91" t="s">
+      <c r="E2" s="128" t="s">
         <v>285</v>
       </c>
-      <c r="F2" s="91"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="93" t="s">
+      <c r="F2" s="128"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="130" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="94"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="101" t="str">
+      <c r="J2" s="131"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="138" t="str">
         <f ca="1">IFERROR(INDEX(#REF!,MATCH(N2,#REF!,0),2)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M2" s="102"/>
-      <c r="N2" s="99" t="str">
+      <c r="M2" s="139"/>
+      <c r="N2" s="136" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,255)</f>
         <v>LKS 01</v>
       </c>
@@ -5512,25 +5512,25 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="2" customFormat="1" ht="43.8">
+    <row r="3" spans="1:23" s="2" customFormat="1" ht="45">
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="111" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="100"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="139"/>
+      <c r="N3" s="137"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -5549,30 +5549,30 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="2" customFormat="1" ht="49.2">
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="50.25">
       <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="113" t="s">
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
-      <c r="L4" s="116" t="str">
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="115" t="str">
         <f ca="1">IFERROR(VLOOKUP($N$2&amp;"_"&amp;$A$6,#REF!,6,0)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M4" s="117"/>
-      <c r="N4" s="118"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117"/>
       <c r="T4" s="33" t="s">
         <v>1</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="5" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A5" s="22" t="s">
         <v>10</v>
       </c>
@@ -5607,11 +5607,11 @@
       <c r="F5" s="72" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="90" t="s">
+      <c r="G5" s="111" t="s">
         <v>202</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
       <c r="J5" s="22" t="s">
         <v>163</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="6" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A6" s="22">
         <v>1</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="7" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A7" s="22">
         <v>2</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="8" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A8" s="22">
         <v>3</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="9" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A9" s="22">
         <v>4</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="10" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A10" s="22">
         <v>5</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="11" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A11" s="22">
         <v>6</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="12" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A12" s="22">
         <v>7</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="13" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A13" s="22">
         <v>8</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="14" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A14" s="22">
         <v>9</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
+    <row r="15" spans="1:23" s="2" customFormat="1" ht="41.25">
       <c r="A15" s="22">
         <v>10</v>
       </c>
@@ -6193,12 +6193,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="2" customFormat="1" ht="40.200000000000003">
-      <c r="A16" s="90" t="s">
+    <row r="16" spans="1:23" s="2" customFormat="1" ht="41.25">
+      <c r="A16" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
       <c r="D16" s="4">
         <f ca="1">SUM(D6:D15)</f>
         <v>1</v>
@@ -6220,45 +6220,45 @@
       <c r="M16" s="13"/>
       <c r="N16" s="14"/>
     </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" ht="52.8">
-      <c r="A17" s="104" t="s">
+    <row r="17" spans="1:14" s="2" customFormat="1" ht="54">
+      <c r="A17" s="118" t="s">
         <v>172</v>
       </c>
-      <c r="B17" s="104"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104" t="s">
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118" t="s">
         <v>171</v>
       </c>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="90" t="s">
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="M17" s="107"/>
+      <c r="M17" s="121"/>
       <c r="N17" s="75">
         <f ca="1">SUM(N6:N16)</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A18" s="105" t="s">
-        <v>289</v>
-      </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="111"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111"/>
+    <row r="18" spans="1:14" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A18" s="119" t="s">
+        <v>288</v>
+      </c>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="125"/>
+      <c r="K18" s="125"/>
       <c r="L18" s="78" t="s">
         <v>16</v>
       </c>
@@ -6271,18 +6271,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.8">
-      <c r="A19" s="104"/>
-      <c r="B19" s="104"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="111"/>
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="54">
+      <c r="A19" s="118"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
       <c r="L19" s="78" t="s">
         <v>204</v>
       </c>
@@ -6295,18 +6295,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" ht="52.8">
-      <c r="A20" s="104"/>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
+    <row r="20" spans="1:14" s="2" customFormat="1" ht="54">
+      <c r="A20" s="118"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
       <c r="L20" s="78" t="s">
         <v>205</v>
       </c>
@@ -6319,19 +6319,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="52.8">
-      <c r="A21" s="104"/>
-      <c r="B21" s="104"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="108" t="s">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="54">
+      <c r="A21" s="118"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="125"/>
+      <c r="L21" s="122" t="s">
         <v>173</v>
       </c>
       <c r="M21" s="69" t="s">
@@ -6342,19 +6342,19 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="52.8">
-      <c r="A22" s="104"/>
-      <c r="B22" s="104"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="109"/>
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="54">
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="125"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="123"/>
       <c r="M22" s="70" t="s">
         <v>18</v>
       </c>
@@ -6363,19 +6363,19 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="52.8">
-      <c r="A23" s="104"/>
-      <c r="B23" s="104"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="109"/>
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="54">
+      <c r="A23" s="118"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="123"/>
       <c r="M23" s="71" t="s">
         <v>19</v>
       </c>
@@ -6384,19 +6384,19 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="52.8">
-      <c r="A24" s="106"/>
-      <c r="B24" s="106"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="112"/>
-      <c r="G24" s="112"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="110"/>
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="54">
+      <c r="A24" s="120"/>
+      <c r="B24" s="120"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="126"/>
+      <c r="J24" s="126"/>
+      <c r="K24" s="126"/>
+      <c r="L24" s="124"/>
       <c r="M24" s="84" t="s">
         <v>20</v>
       </c>
@@ -6421,165 +6421,165 @@
       <c r="M25" s="86"/>
       <c r="N25" s="86"/>
     </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.6">
-      <c r="A26" s="122" t="s">
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="39">
+      <c r="A26" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="B26" s="122"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="122"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="122"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="122"/>
-      <c r="J26" s="122"/>
-      <c r="K26" s="122"/>
-      <c r="L26" s="122"/>
-      <c r="M26" s="122"/>
-      <c r="N26" s="122"/>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="37.799999999999997">
-      <c r="A27" s="119" t="s">
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+    </row>
+    <row r="27" spans="1:14" s="2" customFormat="1" ht="37.5">
+      <c r="A27" s="89" t="s">
         <v>206</v>
       </c>
-      <c r="B27" s="119"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="119"/>
-      <c r="N27" s="119"/>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.6">
-      <c r="A28" s="138" t="s">
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
+      <c r="L27" s="89"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="89"/>
+    </row>
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="39">
+      <c r="A28" s="108" t="s">
+        <v>286</v>
+      </c>
+      <c r="B28" s="108"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="108"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="108"/>
+      <c r="N28" s="108"/>
+    </row>
+    <row r="29" spans="1:14" s="2" customFormat="1" ht="37.5">
+      <c r="A29" s="89" t="s">
         <v>287</v>
       </c>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="138"/>
-      <c r="M28" s="138"/>
-      <c r="N28" s="138"/>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="37.799999999999997">
-      <c r="A29" s="119" t="s">
-        <v>288</v>
-      </c>
-      <c r="B29" s="119"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="119"/>
-      <c r="L29" s="119"/>
-      <c r="M29" s="119"/>
-      <c r="N29" s="119"/>
-    </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" ht="40.200000000000003">
-      <c r="A30" s="123" t="s">
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="89"/>
+    </row>
+    <row r="30" spans="1:14" s="2" customFormat="1" ht="41.25">
+      <c r="A30" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="124"/>
-      <c r="C30" s="129"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="131"/>
+      <c r="B30" s="94"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="101"/>
       <c r="F30" s="26"/>
       <c r="G30" s="15"/>
-      <c r="H30" s="139" t="s">
+      <c r="H30" s="109" t="s">
         <v>174</v>
       </c>
-      <c r="I30" s="139"/>
-      <c r="J30" s="140"/>
-      <c r="K30" s="120" t="s">
+      <c r="I30" s="109"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
-      <c r="N30" s="121"/>
-    </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" ht="40.200000000000003">
-      <c r="A31" s="125"/>
-      <c r="B31" s="126"/>
-      <c r="C31" s="132"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="134"/>
+      <c r="L30" s="91"/>
+      <c r="M30" s="91"/>
+      <c r="N30" s="91"/>
+    </row>
+    <row r="31" spans="1:14" s="2" customFormat="1" ht="41.25">
+      <c r="A31" s="95"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="104"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
       <c r="H31" s="26"/>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
-      <c r="K31" s="120"/>
-      <c r="L31" s="121"/>
-      <c r="M31" s="121"/>
-      <c r="N31" s="121"/>
-    </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" ht="40.200000000000003">
-      <c r="A32" s="125"/>
-      <c r="B32" s="126"/>
-      <c r="C32" s="132"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="134"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="91"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="91"/>
+    </row>
+    <row r="32" spans="1:14" s="2" customFormat="1" ht="41.25">
+      <c r="A32" s="95"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="104"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
       <c r="H32" s="26"/>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
-      <c r="K32" s="120"/>
-      <c r="L32" s="121"/>
-      <c r="M32" s="121"/>
-      <c r="N32" s="121"/>
-    </row>
-    <row r="33" spans="1:22" s="2" customFormat="1" ht="40.200000000000003">
-      <c r="A33" s="125"/>
-      <c r="B33" s="126"/>
-      <c r="C33" s="132"/>
-      <c r="D33" s="133"/>
-      <c r="E33" s="134"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+    </row>
+    <row r="33" spans="1:22" s="2" customFormat="1" ht="41.25">
+      <c r="A33" s="95"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="104"/>
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
-      <c r="K33" s="120"/>
-      <c r="L33" s="121"/>
-      <c r="M33" s="121"/>
-      <c r="N33" s="121"/>
-    </row>
-    <row r="34" spans="1:22" s="2" customFormat="1" ht="40.200000000000003">
-      <c r="A34" s="127"/>
-      <c r="B34" s="128"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="137"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
+      <c r="N33" s="91"/>
+    </row>
+    <row r="34" spans="1:22" s="2" customFormat="1" ht="41.25">
+      <c r="A34" s="97"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="106"/>
+      <c r="E34" s="107"/>
       <c r="F34" s="26"/>
       <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
-      <c r="K34" s="120"/>
-      <c r="L34" s="121"/>
-      <c r="M34" s="121"/>
-      <c r="N34" s="121"/>
-    </row>
-    <row r="35" spans="1:22" s="2" customFormat="1" ht="30">
+      <c r="K34" s="90"/>
+      <c r="L34" s="91"/>
+      <c r="M34" s="91"/>
+      <c r="N34" s="91"/>
+    </row>
+    <row r="35" spans="1:22" s="2" customFormat="1" ht="31.5">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="16"/>
@@ -6595,7 +6595,7 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:22" s="2" customFormat="1" ht="30">
+    <row r="36" spans="1:22" s="2" customFormat="1" ht="31.5">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -6613,8 +6613,8 @@
     </row>
     <row r="37" spans="1:22" ht="16.5" customHeight="1"/>
     <row r="38" spans="1:22" ht="16.5" customHeight="1"/>
-    <row r="41" spans="1:22" ht="24.9" customHeight="1"/>
-    <row r="42" spans="1:22" ht="24.9" customHeight="1">
+    <row r="41" spans="1:22" ht="24.95" customHeight="1"/>
+    <row r="42" spans="1:22" ht="24.95" customHeight="1">
       <c r="Q42" s="18"/>
       <c r="R42" s="18"/>
       <c r="S42" s="18"/>
@@ -6622,28 +6622,28 @@
       <c r="U42" s="18"/>
       <c r="V42" s="18"/>
     </row>
-    <row r="43" spans="1:22" ht="24.9" customHeight="1">
+    <row r="43" spans="1:22" ht="24.95" customHeight="1">
       <c r="Q43" s="19"/>
     </row>
-    <row r="44" spans="1:22" ht="24.9" customHeight="1">
+    <row r="44" spans="1:22" ht="24.95" customHeight="1">
       <c r="Q44" s="19"/>
     </row>
-    <row r="45" spans="1:22" ht="24.9" customHeight="1">
+    <row r="45" spans="1:22" ht="24.95" customHeight="1">
       <c r="Q45" s="19"/>
     </row>
-    <row r="46" spans="1:22" ht="24.9" customHeight="1">
+    <row r="46" spans="1:22" ht="24.95" customHeight="1">
       <c r="Q46" s="19"/>
     </row>
-    <row r="47" spans="1:22" ht="24.9" customHeight="1">
+    <row r="47" spans="1:22" ht="24.95" customHeight="1">
       <c r="Q47" s="19"/>
     </row>
-    <row r="48" spans="1:22" ht="24.9" customHeight="1">
+    <row r="48" spans="1:22" ht="24.95" customHeight="1">
       <c r="Q48" s="19"/>
     </row>
-    <row r="49" spans="17:17" ht="24.9" customHeight="1">
+    <row r="49" spans="17:17" ht="24.95" customHeight="1">
       <c r="Q49" s="19"/>
     </row>
-    <row r="50" spans="17:17" ht="24.9" customHeight="1">
+    <row r="50" spans="17:17" ht="24.95" customHeight="1">
       <c r="Q50" s="19"/>
     </row>
     <row r="51" spans="17:17" ht="30" customHeight="1"/>
@@ -6664,6 +6664,25 @@
     <row r="66" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E24"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L21:L24"/>
+    <mergeCell ref="F17:K17"/>
+    <mergeCell ref="F18:K24"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
     <mergeCell ref="A27:N27"/>
     <mergeCell ref="K30:K34"/>
     <mergeCell ref="L30:N34"/>
@@ -6673,25 +6692,6 @@
     <mergeCell ref="A29:N29"/>
     <mergeCell ref="A28:N28"/>
     <mergeCell ref="H30:J30"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E24"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L21:L24"/>
-    <mergeCell ref="F17:K17"/>
-    <mergeCell ref="F18:K24"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C1:K1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="L6:L15">
@@ -6708,7 +6708,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="27" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="25" fitToWidth="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
